--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9438,0.0579,0.0050,0.0007</t>
-  </si>
-  <si>
-    <t>0.9446,0.0162,0.0217,0.0047</t>
-  </si>
-  <si>
-    <t>0.8920,0.1007,0.0074,0.0019</t>
-  </si>
-  <si>
-    <t>0.9653,0.0175,0.0059,0.0013</t>
-  </si>
-  <si>
-    <t>0.7979,0.2633,0.0171,0.0012</t>
-  </si>
-  <si>
-    <t>0.9512,0.0310,0.0013,0.0016</t>
-  </si>
-  <si>
-    <t>0.7736,0.3053,0.0160,0.0011</t>
-  </si>
-  <si>
-    <t>0.9246,0.0766,0.0038,0.0015</t>
-  </si>
-  <si>
-    <t>0.9445,0.0641,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9150,0.0933,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.9580,0.0296,0.0027,0.0017</t>
-  </si>
-  <si>
-    <t>0.9444,0.0450,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.9848,0.0059,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9411,0.0378,0.0239,0.0004</t>
-  </si>
-  <si>
-    <t>0.9782,0.0072,0.0122,0.0002</t>
-  </si>
-  <si>
-    <t>0.9790,0.0034,0.0236,0.0003</t>
-  </si>
-  <si>
-    <t>0.9275,0.0589,0.0183,0.0006</t>
-  </si>
-  <si>
-    <t>0.6377,0.5425,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.9100,0.0968,0.0101,0.0008</t>
-  </si>
-  <si>
-    <t>0.6374,0.4857,0.0098,0.0009</t>
-  </si>
-  <si>
-    <t>0.3171,0.7836,0.0255,0.0005</t>
-  </si>
-  <si>
-    <t>0.6224,0.5318,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9452,0.0174,0.0356,0.0007</t>
-  </si>
-  <si>
-    <t>0.9841,0.0029,0.0108,0.0004</t>
-  </si>
-  <si>
-    <t>0.9554,0.0059,0.0682,0.0008</t>
-  </si>
-  <si>
-    <t>0.9738,0.0051,0.0182,0.0003</t>
-  </si>
-  <si>
-    <t>0.9282,0.0039,0.1475,0.0011</t>
-  </si>
-  <si>
-    <t>0.8612,0.0100,0.2209,0.0027</t>
-  </si>
-  <si>
-    <t>0.6194,0.0061,0.5501,0.0004</t>
-  </si>
-  <si>
-    <t>0.9359,0.0614,0.0096,0.0006</t>
-  </si>
-  <si>
-    <t>0.8577,0.1438,0.0232,0.0010</t>
-  </si>
-  <si>
-    <t>0.1990,0.0500,0.8290,0.0016</t>
-  </si>
-  <si>
-    <t>0.8809,0.1215,0.0073,0.0000</t>
-  </si>
-  <si>
-    <t>0.8988,0.0793,0.0083,0.0019</t>
-  </si>
-  <si>
-    <t>0.8810,0.0778,0.0134,0.0035</t>
-  </si>
-  <si>
-    <t>0.8338,0.1753,0.0106,0.0021</t>
-  </si>
-  <si>
-    <t>0.9908,0.0061,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.7482,0.0704,0.2482,0.0041</t>
-  </si>
-  <si>
-    <t>0.9851,0.0003,0.0262,0.0003</t>
-  </si>
-  <si>
-    <t>0.9732,0.0018,0.0364,0.0002</t>
-  </si>
-  <si>
-    <t>0.9639,0.0030,0.0483,0.0006</t>
-  </si>
-  <si>
-    <t>0.8121,0.0153,0.2021,0.0005</t>
-  </si>
-  <si>
-    <t>0.5253,0.4112,0.0123,0.0001</t>
-  </si>
-  <si>
-    <t>0.9510,0.0023,0.0902,0.0003</t>
-  </si>
-  <si>
-    <t>0.7895,0.2124,0.0274,0.0028</t>
-  </si>
-  <si>
-    <t>0.6772,0.3441,0.0124,0.0001</t>
-  </si>
-  <si>
-    <t>0.9543,0.0533,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0096,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.1862,0.0120,0.8718,0.0035</t>
-  </si>
-  <si>
-    <t>0.6680,0.0060,0.5302,0.0007</t>
-  </si>
-  <si>
-    <t>0.7478,0.0131,0.3600,0.0014</t>
-  </si>
-  <si>
-    <t>0.9273,0.0029,0.1197,0.0022</t>
-  </si>
-  <si>
-    <t>0.0320,0.0072,0.9826,0.0003</t>
-  </si>
-  <si>
-    <t>0.6956,0.0164,0.3546,0.0014</t>
-  </si>
-  <si>
-    <t>0.6666,0.4223,0.0219,0.0018</t>
-  </si>
-  <si>
-    <t>0.8564,0.1406,0.0094,0.0025</t>
-  </si>
-  <si>
-    <t>0.8326,0.1683,0.0111,0.0032</t>
-  </si>
-  <si>
-    <t>0.0868,0.7475,0.5899,0.0079</t>
-  </si>
-  <si>
-    <t>0.9569,0.0321,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.6296,0.5053,0.0108,0.0008</t>
-  </si>
-  <si>
-    <t>0.8830,0.1593,0.0057,0.0010</t>
-  </si>
-  <si>
-    <t>0.2376,0.5385,0.5329,0.0093</t>
-  </si>
-  <si>
-    <t>0.0769,0.0106,0.9628,0.0006</t>
-  </si>
-  <si>
-    <t>0.8077,0.0236,0.2539,0.0013</t>
-  </si>
-  <si>
-    <t>0.3589,0.0450,0.6904,0.0008</t>
-  </si>
-  <si>
-    <t>0.1767,0.0071,0.9049,0.0022</t>
-  </si>
-  <si>
-    <t>0.9282,0.0611,0.0220,0.0005</t>
-  </si>
-  <si>
-    <t>0.6931,0.4446,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.8818,0.0896,0.0267,0.0011</t>
-  </si>
-  <si>
-    <t>0.8725,0.1803,0.0066,0.0004</t>
-  </si>
-  <si>
-    <t>0.0180,0.4368,0.9320,0.0043</t>
-  </si>
-  <si>
-    <t>0.9408,0.0084,0.0765,0.0004</t>
-  </si>
-  <si>
-    <t>0.6719,0.0623,0.2704,0.0004</t>
-  </si>
-  <si>
-    <t>0.4625,0.6003,0.0179,0.0002</t>
-  </si>
-  <si>
-    <t>0.2650,0.0578,0.7423,0.0008</t>
-  </si>
-  <si>
-    <t>0.9684,0.0097,0.0036,0.0033</t>
-  </si>
-  <si>
-    <t>0.9668,0.0054,0.0071,0.0057</t>
-  </si>
-  <si>
-    <t>0.9720,0.0032,0.0076,0.0041</t>
-  </si>
-  <si>
-    <t>0.9733,0.0108,0.0037,0.0015</t>
-  </si>
-  <si>
-    <t>0.9834,0.0037,0.0036,0.0016</t>
-  </si>
-  <si>
-    <t>0.9884,0.0025,0.0023,0.0010</t>
-  </si>
-  <si>
-    <t>0.6259,0.1001,0.3043,0.0006</t>
-  </si>
-  <si>
-    <t>0.5293,0.0014,0.7377,0.0002</t>
-  </si>
-  <si>
-    <t>0.3977,0.1246,0.5239,0.0018</t>
-  </si>
-  <si>
-    <t>0.9205,0.0033,0.1575,0.0005</t>
-  </si>
-  <si>
-    <t>0.4773,0.1105,0.3490,0.0006</t>
-  </si>
-  <si>
-    <t>0.9301,0.0159,0.0386,0.0002</t>
-  </si>
-  <si>
-    <t>0.9219,0.1038,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.6401,0.4135,0.0422,0.0053</t>
-  </si>
-  <si>
-    <t>0.9799,0.0126,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9260,0.0743,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.8125,0.1801,0.0184,0.0060</t>
-  </si>
-  <si>
-    <t>0.8766,0.1484,0.0050,0.0013</t>
-  </si>
-  <si>
-    <t>0.9353,0.0713,0.0042,0.0011</t>
-  </si>
-  <si>
-    <t>0.8672,0.1180,0.0044,0.0029</t>
-  </si>
-  <si>
-    <t>0.8816,0.1702,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.9426,0.0542,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.9865,0.0084,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.8329,0.2122,0.0074,0.0014</t>
-  </si>
-  <si>
-    <t>0.8873,0.1199,0.0181,0.0023</t>
-  </si>
-  <si>
-    <t>0.9639,0.0361,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9343,0.0519,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.9202,0.0545,0.0078,0.0035</t>
-  </si>
-  <si>
-    <t>0.0311,0.0484,0.9725,0.0028</t>
-  </si>
-  <si>
-    <t>0.4185,0.0130,0.7453,0.0021</t>
-  </si>
-  <si>
-    <t>0.9888,0.0023,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.9838,0.0028,0.0146,0.0003</t>
-  </si>
-  <si>
-    <t>0.6114,0.5750,0.0082,0.0002</t>
-  </si>
-  <si>
-    <t>0.0437,0.9632,0.0100,0.0002</t>
-  </si>
-  <si>
-    <t>0.8875,0.1529,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.8873,0.1493,0.0053,0.0009</t>
-  </si>
-  <si>
-    <t>0.6898,0.5125,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.2709,0.8335,0.0148,0.0004</t>
-  </si>
-  <si>
-    <t>0.9195,0.1117,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.8662,0.1075,0.0277,0.0019</t>
-  </si>
-  <si>
-    <t>0.9493,0.0103,0.0464,0.0014</t>
-  </si>
-  <si>
-    <t>0.9720,0.0071,0.0145,0.0004</t>
-  </si>
-  <si>
-    <t>0.9783,0.0085,0.0096,0.0003</t>
-  </si>
-  <si>
-    <t>0.9474,0.0300,0.0114,0.0023</t>
-  </si>
-  <si>
-    <t>0.9680,0.0273,0.0039,0.0000</t>
-  </si>
-  <si>
-    <t>0.9613,0.0472,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9774,0.0183,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.1635,0.0797,0.5205,0.0004</t>
-  </si>
-  <si>
-    <t>0.9127,0.1249,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9579,0.0238,0.0080,0.0006</t>
-  </si>
-  <si>
-    <t>0.7821,0.2748,0.0139,0.0017</t>
-  </si>
-  <si>
-    <t>0.8207,0.2303,0.0110,0.0012</t>
-  </si>
-  <si>
-    <t>0.8769,0.1237,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.9110,0.0979,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.9377,0.0462,0.0055,0.0014</t>
-  </si>
-  <si>
-    <t>0.9608,0.0294,0.0037,0.0010</t>
-  </si>
-  <si>
-    <t>0.9389,0.0532,0.0128,0.0010</t>
-  </si>
-  <si>
-    <t>0.6314,0.4450,0.0130,0.0016</t>
-  </si>
-  <si>
-    <t>0.9464,0.0667,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9020,0.0071,0.1543,0.0005</t>
-  </si>
-  <si>
-    <t>0.8322,0.0023,0.3719,0.0002</t>
-  </si>
-  <si>
-    <t>0.8206,0.0141,0.2059,0.0012</t>
-  </si>
-  <si>
-    <t>0.9872,0.0006,0.0260,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0023,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9521,0.0232,0.0121,0.0008</t>
-  </si>
-  <si>
-    <t>0.9731,0.0061,0.0144,0.0005</t>
-  </si>
-  <si>
-    <t>0.9600,0.0160,0.0201,0.0005</t>
-  </si>
-  <si>
-    <t>0.9680,0.0103,0.0060,0.0027</t>
-  </si>
-  <si>
-    <t>0.6652,0.0144,0.0575,0.2431</t>
-  </si>
-  <si>
-    <t>0.9692,0.0057,0.0163,0.0026</t>
-  </si>
-  <si>
-    <t>0.9794,0.0077,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.1723,0.2629,0.4763,0.0003</t>
-  </si>
-  <si>
-    <t>0.8299,0.1976,0.0115,0.0027</t>
-  </si>
-  <si>
-    <t>0.5246,0.4797,0.0457,0.0015</t>
-  </si>
-  <si>
-    <t>0.8593,0.1439,0.0140,0.0038</t>
-  </si>
-  <si>
-    <t>0.5483,0.5802,0.0164,0.0014</t>
-  </si>
-  <si>
-    <t>0.9346,0.0507,0.0067,0.0013</t>
-  </si>
-  <si>
-    <t>0.9023,0.0739,0.0105,0.0026</t>
-  </si>
-  <si>
-    <t>0.9143,0.0817,0.0053,0.0025</t>
-  </si>
-  <si>
-    <t>0.2314,0.2025,0.7712,0.0457</t>
-  </si>
-  <si>
-    <t>0.9612,0.0178,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.9051,0.0709,0.0068,0.0023</t>
-  </si>
-  <si>
-    <t>0.9414,0.0751,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9420,0.0494,0.0043,0.0012</t>
-  </si>
-  <si>
-    <t>0.9649,0.0304,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0036,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.8608,0.1289,0.0179,0.0003</t>
-  </si>
-  <si>
-    <t>0.9772,0.0147,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9582,0.0309,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.8598,0.1389,0.0036,0.0019</t>
-  </si>
-  <si>
-    <t>0.9387,0.0590,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.6625,0.3814,0.0067,0.0020</t>
-  </si>
-  <si>
-    <t>0.9090,0.0788,0.0053,0.0010</t>
-  </si>
-  <si>
-    <t>0.4918,0.5928,0.0140,0.0022</t>
-  </si>
-  <si>
-    <t>0.8919,0.0962,0.0061,0.0019</t>
-  </si>
-  <si>
-    <t>0.9174,0.0832,0.0057,0.0013</t>
-  </si>
-  <si>
-    <t>0.9391,0.0678,0.0049,0.0009</t>
-  </si>
-  <si>
-    <t>0.5884,0.5077,0.0254,0.0026</t>
-  </si>
-  <si>
-    <t>0.9516,0.0371,0.0039,0.0007</t>
-  </si>
-  <si>
-    <t>0.8156,0.2082,0.0128,0.0014</t>
-  </si>
-  <si>
-    <t>0.7204,0.3823,0.0083,0.0017</t>
-  </si>
-  <si>
-    <t>0.9827,0.0139,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.8739,0.2028,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9523,0.0428,0.0034,0.0008</t>
-  </si>
-  <si>
-    <t>0.2913,0.4710,0.1166,0.0001</t>
-  </si>
-  <si>
-    <t>0.6281,0.4236,0.0348,0.0041</t>
-  </si>
-  <si>
-    <t>0.3363,0.0049,0.7609,0.0004</t>
-  </si>
-  <si>
-    <t>0.8375,0.0018,0.3420,0.0006</t>
-  </si>
-  <si>
-    <t>0.4727,0.0379,0.5946,0.0030</t>
-  </si>
-  <si>
-    <t>0.0977,0.1701,0.7731,0.0003</t>
-  </si>
-  <si>
-    <t>0.7817,0.0042,0.4537,0.0003</t>
-  </si>
-  <si>
-    <t>0.9125,0.0030,0.1571,0.0003</t>
-  </si>
-  <si>
-    <t>0.3103,0.0454,0.7672,0.0033</t>
-  </si>
-  <si>
-    <t>0.8787,0.0392,0.0892,0.0020</t>
-  </si>
-  <si>
-    <t>0.9240,0.0332,0.0301,0.0003</t>
-  </si>
-  <si>
-    <t>0.9289,0.0372,0.0282,0.0009</t>
-  </si>
-  <si>
-    <t>0.9672,0.0142,0.0136,0.0002</t>
-  </si>
-  <si>
-    <t>0.8225,0.0728,0.0988,0.0024</t>
-  </si>
-  <si>
-    <t>0.9722,0.0052,0.0196,0.0003</t>
-  </si>
-  <si>
-    <t>0.9215,0.0502,0.0181,0.0009</t>
-  </si>
-  <si>
-    <t>0.9864,0.0041,0.0074,0.0003</t>
-  </si>
-  <si>
-    <t>0.5016,0.6215,0.0165,0.0012</t>
-  </si>
-  <si>
-    <t>0.5764,0.6096,0.0036,0.0009</t>
-  </si>
-  <si>
-    <t>0.9472,0.0471,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.6133,0.4147,0.0390,0.0045</t>
-  </si>
-  <si>
-    <t>0.9377,0.0740,0.0046,0.0007</t>
-  </si>
-  <si>
-    <t>0.9832,0.0051,0.0063,0.0003</t>
-  </si>
-  <si>
-    <t>0.9689,0.0115,0.0125,0.0004</t>
-  </si>
-  <si>
-    <t>0.9823,0.0034,0.0153,0.0003</t>
-  </si>
-  <si>
-    <t>0.9496,0.0095,0.0435,0.0008</t>
-  </si>
-  <si>
-    <t>0.9711,0.0114,0.0121,0.0004</t>
-  </si>
-  <si>
-    <t>0.0320,0.3480,0.8654,0.0010</t>
-  </si>
-  <si>
-    <t>0.9756,0.0025,0.0348,0.0003</t>
-  </si>
-  <si>
-    <t>0.9182,0.0209,0.0622,0.0009</t>
-  </si>
-  <si>
-    <t>0.9878,0.0005,0.0214,0.0001</t>
-  </si>
-  <si>
-    <t>0.9896,0.0005,0.0181,0.0001</t>
-  </si>
-  <si>
-    <t>0.9461,0.0489,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.9218,0.0889,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.9465,0.0364,0.0031,0.0018</t>
-  </si>
-  <si>
-    <t>0.8842,0.1538,0.0065,0.0008</t>
-  </si>
-  <si>
-    <t>0.8383,0.1612,0.0061,0.0023</t>
-  </si>
-  <si>
-    <t>0.8434,0.1786,0.0094,0.0024</t>
-  </si>
-  <si>
-    <t>0.8823,0.1176,0.0047,0.0017</t>
-  </si>
-  <si>
-    <t>0.5986,0.4558,0.0277,0.0038</t>
-  </si>
-  <si>
-    <t>0.7314,0.1229,0.1368,0.0023</t>
-  </si>
-  <si>
-    <t>0.9007,0.1092,0.0088,0.0007</t>
-  </si>
-  <si>
-    <t>0.9685,0.0187,0.0053,0.0012</t>
-  </si>
-  <si>
-    <t>0.7227,0.0134,0.3798,0.0009</t>
-  </si>
-  <si>
-    <t>0.0091,0.0970,0.9775,0.0008</t>
-  </si>
-  <si>
-    <t>0.8135,0.0230,0.1726,0.0015</t>
-  </si>
-  <si>
-    <t>0.2630,0.0100,0.8758,0.0014</t>
-  </si>
-  <si>
-    <t>0.8482,0.0060,0.2833,0.0006</t>
-  </si>
-  <si>
-    <t>0.0105,0.0596,0.9783,0.0015</t>
-  </si>
-  <si>
-    <t>0.5427,0.0072,0.6419,0.0017</t>
-  </si>
-  <si>
-    <t>0.9097,0.0240,0.0586,0.0007</t>
-  </si>
-  <si>
-    <t>0.9889,0.0011,0.0109,0.0002</t>
-  </si>
-  <si>
-    <t>0.9699,0.0054,0.0260,0.0003</t>
-  </si>
-  <si>
-    <t>0.9732,0.0144,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.8179,0.1829,0.0087,0.0023</t>
-  </si>
-  <si>
-    <t>0.9102,0.0667,0.0074,0.0044</t>
-  </si>
-  <si>
-    <t>0.8951,0.1310,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.9261,0.0979,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.9697,0.0247,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.8978,0.1020,0.0046,0.0017</t>
-  </si>
-  <si>
-    <t>0.7881,0.3038,0.0058,0.0007</t>
-  </si>
-  <si>
-    <t>0.8019,0.2813,0.0044,0.0008</t>
-  </si>
-  <si>
-    <t>0.9579,0.0056,0.0442,0.0002</t>
-  </si>
-  <si>
-    <t>0.6652,0.0029,0.5518,0.0005</t>
-  </si>
-  <si>
-    <t>0.6747,0.0093,0.3268,0.0006</t>
-  </si>
-  <si>
-    <t>0.7669,0.0187,0.3387,0.0032</t>
-  </si>
-  <si>
-    <t>0.9004,0.0040,0.1742,0.0013</t>
-  </si>
-  <si>
-    <t>0.9713,0.0039,0.0285,0.0005</t>
-  </si>
-  <si>
-    <t>0.9715,0.0036,0.0332,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0003,0.0098,0.0001</t>
-  </si>
-  <si>
-    <t>0.9897,0.0029,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9761,0.0084,0.0077,0.0007</t>
-  </si>
-  <si>
-    <t>0.9735,0.0062,0.0040,0.0047</t>
-  </si>
-  <si>
-    <t>0.9189,0.0337,0.0201,0.0070</t>
-  </si>
-  <si>
-    <t>0.9474,0.0169,0.0079,0.0098</t>
-  </si>
-  <si>
-    <t>0.8505,0.1802,0.0050,0.0006</t>
+    <t>0.9323,0.0112,0.0093,0.0310</t>
+  </si>
+  <si>
+    <t>0.0163,0.0011,0.0027,0.9896</t>
+  </si>
+  <si>
+    <t>0.7172,0.0015,0.0002,0.3856</t>
+  </si>
+  <si>
+    <t>0.0177,0.0044,0.0029,0.9895</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9902,0.0074,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9871,0.0055,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9959,0.0013,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9653,0.0071,0.0224,0.0022</t>
+  </si>
+  <si>
+    <t>0.0085,0.0011,0.9899,0.0013</t>
+  </si>
+  <si>
+    <t>0.0240,0.0316,0.9650,0.0007</t>
+  </si>
+  <si>
+    <t>0.0294,0.0009,0.9694,0.0021</t>
+  </si>
+  <si>
+    <t>0.9447,0.0040,0.0950,0.0006</t>
+  </si>
+  <si>
+    <t>0.0165,0.9796,0.0038,0.0037</t>
+  </si>
+  <si>
+    <t>0.0045,0.9892,0.0039,0.0051</t>
+  </si>
+  <si>
+    <t>0.3736,0.7385,0.0059,0.0023</t>
+  </si>
+  <si>
+    <t>0.0303,0.9769,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.0012,0.9960,0.0120,0.0010</t>
+  </si>
+  <si>
+    <t>0.9131,0.0015,0.1128,0.0048</t>
+  </si>
+  <si>
+    <t>0.5788,0.0012,0.5273,0.0043</t>
+  </si>
+  <si>
+    <t>0.0073,0.0031,0.9860,0.0027</t>
+  </si>
+  <si>
+    <t>0.0696,0.0218,0.8945,0.0092</t>
+  </si>
+  <si>
+    <t>0.0273,0.0082,0.9754,0.0016</t>
+  </si>
+  <si>
+    <t>0.0935,0.0020,0.9440,0.0021</t>
+  </si>
+  <si>
+    <t>0.0131,0.0009,0.9878,0.0008</t>
+  </si>
+  <si>
+    <t>0.4216,0.6683,0.0060,0.0123</t>
+  </si>
+  <si>
+    <t>0.8195,0.1643,0.0430,0.0074</t>
+  </si>
+  <si>
+    <t>0.0030,0.0060,0.9938,0.0031</t>
+  </si>
+  <si>
+    <t>0.0410,0.8185,0.1044,0.0004</t>
+  </si>
+  <si>
+    <t>0.7749,0.1891,0.0149,0.0433</t>
+  </si>
+  <si>
+    <t>0.8142,0.1509,0.0274,0.0173</t>
+  </si>
+  <si>
+    <t>0.9354,0.1018,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.0394,0.9264,0.3323,0.0024</t>
+  </si>
+  <si>
+    <t>0.0473,0.0949,0.8183,0.0279</t>
+  </si>
+  <si>
+    <t>0.2203,0.0162,0.8331,0.0087</t>
+  </si>
+  <si>
+    <t>0.0132,0.0248,0.9730,0.0079</t>
+  </si>
+  <si>
+    <t>0.4410,0.0013,0.5815,0.0096</t>
+  </si>
+  <si>
+    <t>0.0017,0.0521,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0160,0.7519,0.1690,0.0020</t>
+  </si>
+  <si>
+    <t>0.0072,0.0017,0.9907,0.0012</t>
+  </si>
+  <si>
+    <t>0.3169,0.2180,0.0167,0.5401</t>
+  </si>
+  <si>
+    <t>0.0012,0.9942,0.0022,0.0040</t>
+  </si>
+  <si>
+    <t>0.0036,0.9915,0.0077,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.9959,0.0064,0.0017</t>
+  </si>
+  <si>
+    <t>0.0002,0.0021,0.9964,0.0082</t>
+  </si>
+  <si>
+    <t>0.0010,0.0050,0.9966,0.0014</t>
+  </si>
+  <si>
+    <t>0.0489,0.0049,0.9419,0.0079</t>
+  </si>
+  <si>
+    <t>0.0339,0.0017,0.9771,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.0046,0.9916,0.0081</t>
+  </si>
+  <si>
+    <t>0.0030,0.0121,0.9918,0.0028</t>
+  </si>
+  <si>
+    <t>0.9850,0.0091,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9908,0.0024,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.9930,0.0045,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0279,0.0349,0.9710,0.0094</t>
+  </si>
+  <si>
+    <t>0.9955,0.0008,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9937,0.0025,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9858,0.0140,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.9532,0.9906,0.0003</t>
+  </si>
+  <si>
+    <t>0.0046,0.0027,0.9945,0.0013</t>
+  </si>
+  <si>
+    <t>0.0020,0.0035,0.9959,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9874,0.9808,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.0019,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0897,0.8982,0.0309,0.0027</t>
+  </si>
+  <si>
+    <t>0.0038,0.9954,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.8837,0.0048,0.1703,0.0023</t>
+  </si>
+  <si>
+    <t>0.1330,0.0637,0.8843,0.0018</t>
+  </si>
+  <si>
+    <t>0.0051,0.0273,0.9844,0.0230</t>
+  </si>
+  <si>
+    <t>0.0019,0.9685,0.9091,0.0004</t>
+  </si>
+  <si>
+    <t>0.0084,0.6879,0.9350,0.0042</t>
+  </si>
+  <si>
+    <t>0.0018,0.9826,0.5081,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.9713,0.8240,0.0008</t>
+  </si>
+  <si>
+    <t>0.0054,0.0019,0.0175,0.9878</t>
+  </si>
+  <si>
+    <t>0.0006,0.0087,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0022,0.0059,0.0003,0.9983</t>
+  </si>
+  <si>
+    <t>0.0128,0.0010,0.0017,0.9936</t>
+  </si>
+  <si>
+    <t>0.0017,0.0012,0.0009,0.9984</t>
+  </si>
+  <si>
+    <t>0.0024,0.0184,0.0008,0.9974</t>
+  </si>
+  <si>
+    <t>0.0007,0.9874,0.9330,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.7043,0.9918,0.0006</t>
+  </si>
+  <si>
+    <t>0.0087,0.7389,0.8258,0.0035</t>
+  </si>
+  <si>
+    <t>0.0008,0.8953,0.9909,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.9930,0.9597,0.0001</t>
+  </si>
+  <si>
+    <t>0.0086,0.9595,0.1423,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0027,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9820,0.0113,0.0029,0.0020</t>
+  </si>
+  <si>
+    <t>0.9615,0.0462,0.0038,0.0013</t>
+  </si>
+  <si>
+    <t>0.9946,0.0014,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9916,0.0037,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9900,0.0056,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.9952,0.0025,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9940,0.0019,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.9963,0.0011,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9858,0.0097,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.0084,0.0149,0.9902,0.0023</t>
+  </si>
+  <si>
+    <t>0.0307,0.0050,0.9670,0.0032</t>
+  </si>
+  <si>
+    <t>0.9231,0.0065,0.0720,0.0100</t>
+  </si>
+  <si>
+    <t>0.0021,0.0017,0.9955,0.0013</t>
+  </si>
+  <si>
+    <t>0.0030,0.9940,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.0021,0.9954,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.0550,0.9393,0.0093,0.0069</t>
+  </si>
+  <si>
+    <t>0.5062,0.5798,0.0138,0.0102</t>
+  </si>
+  <si>
+    <t>0.0046,0.9911,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.0175,0.9746,0.0115,0.0016</t>
+  </si>
+  <si>
+    <t>0.2954,0.7810,0.0121,0.0063</t>
+  </si>
+  <si>
+    <t>0.9545,0.0092,0.0326,0.0041</t>
+  </si>
+  <si>
+    <t>0.3992,0.0006,0.7853,0.0007</t>
+  </si>
+  <si>
+    <t>0.5723,0.0190,0.4244,0.0368</t>
+  </si>
+  <si>
+    <t>0.2669,0.0511,0.7335,0.0213</t>
+  </si>
+  <si>
+    <t>0.0124,0.0205,0.3150,0.8598</t>
+  </si>
+  <si>
+    <t>0.0068,0.9881,0.0074,0.0019</t>
+  </si>
+  <si>
+    <t>0.0035,0.9925,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.0202,0.9666,0.0131,0.0111</t>
+  </si>
+  <si>
+    <t>0.0028,0.2816,0.9691,0.0014</t>
+  </si>
+  <si>
+    <t>0.0045,0.9948,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.6402,0.4693,0.0183,0.0037</t>
+  </si>
+  <si>
+    <t>0.9280,0.1035,0.0040,0.0012</t>
+  </si>
+  <si>
+    <t>0.9776,0.0110,0.0025,0.0061</t>
+  </si>
+  <si>
+    <t>0.9964,0.0003,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9927,0.0008,0.0008,0.0029</t>
+  </si>
+  <si>
+    <t>0.9614,0.0112,0.0244,0.0038</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9814,0.0024,0.0184,0.0022</t>
+  </si>
+  <si>
+    <t>0.9766,0.0123,0.0041,0.0028</t>
+  </si>
+  <si>
+    <t>0.9803,0.0088,0.0039,0.0038</t>
+  </si>
+  <si>
+    <t>0.0068,0.9120,0.8255,0.0056</t>
+  </si>
+  <si>
+    <t>0.0010,0.2645,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.0024,0.9874,0.0034</t>
+  </si>
+  <si>
+    <t>0.0095,0.0136,0.9805,0.0058</t>
+  </si>
+  <si>
+    <t>0.9815,0.0027,0.0082,0.0019</t>
+  </si>
+  <si>
+    <t>0.6517,0.0220,0.3481,0.0308</t>
+  </si>
+  <si>
+    <t>0.2345,0.0191,0.7361,0.0481</t>
+  </si>
+  <si>
+    <t>0.8998,0.0039,0.1347,0.0053</t>
+  </si>
+  <si>
+    <t>0.0813,0.0016,0.0018,0.9730</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.0024,0.9993</t>
+  </si>
+  <si>
+    <t>0.0009,0.0091,0.0055,0.9970</t>
+  </si>
+  <si>
+    <t>0.0066,0.0003,0.0003,0.9976</t>
+  </si>
+  <si>
+    <t>0.0016,0.9881,0.0913,0.0019</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.6626,0.3722,0.0036,0.0067</t>
+  </si>
+  <si>
+    <t>0.9900,0.0015,0.0031,0.0033</t>
+  </si>
+  <si>
+    <t>0.8186,0.2337,0.0086,0.0035</t>
+  </si>
+  <si>
+    <t>0.9847,0.0006,0.0026,0.0076</t>
+  </si>
+  <si>
+    <t>0.1752,0.0444,0.0071,0.8647</t>
+  </si>
+  <si>
+    <t>0.9880,0.0043,0.0032,0.0026</t>
+  </si>
+  <si>
+    <t>0.0019,0.0144,0.9486,0.2939</t>
+  </si>
+  <si>
+    <t>0.6470,0.0003,0.0006,0.6669</t>
+  </si>
+  <si>
+    <t>0.9566,0.0013,0.0023,0.0471</t>
+  </si>
+  <si>
+    <t>0.0550,0.9041,0.0253,0.0264</t>
+  </si>
+  <si>
+    <t>0.9389,0.0300,0.0094,0.0125</t>
+  </si>
+  <si>
+    <t>0.9725,0.0137,0.0111,0.0018</t>
+  </si>
+  <si>
+    <t>0.1899,0.6858,0.1676,0.0584</t>
+  </si>
+  <si>
+    <t>0.9771,0.0107,0.0071,0.0011</t>
+  </si>
+  <si>
+    <t>0.9260,0.0754,0.0136,0.0036</t>
+  </si>
+  <si>
+    <t>0.9871,0.0073,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9948,0.0013,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9939,0.0025,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9796,0.0135,0.0017,0.0025</t>
+  </si>
+  <si>
+    <t>0.9905,0.0008,0.0020,0.0054</t>
+  </si>
+  <si>
+    <t>0.9933,0.0006,0.0008,0.0036</t>
+  </si>
+  <si>
+    <t>0.6239,0.3911,0.0021,0.0086</t>
+  </si>
+  <si>
+    <t>0.5337,0.5967,0.0029,0.0027</t>
+  </si>
+  <si>
+    <t>0.7961,0.2683,0.0072,0.0025</t>
+  </si>
+  <si>
+    <t>0.0404,0.4629,0.9346,0.0052</t>
+  </si>
+  <si>
+    <t>0.9906,0.0122,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9744,0.0051,0.0059,0.0069</t>
+  </si>
+  <si>
+    <t>0.9935,0.0028,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9645,0.0394,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.0008,0.0174,0.9986,0.0006</t>
+  </si>
+  <si>
+    <t>0.9316,0.0250,0.0379,0.0074</t>
+  </si>
+  <si>
+    <t>0.0027,0.0011,0.9937,0.0018</t>
+  </si>
+  <si>
+    <t>0.0024,0.1248,0.9768,0.0253</t>
+  </si>
+  <si>
+    <t>0.0065,0.0053,0.9844,0.0107</t>
+  </si>
+  <si>
+    <t>0.0029,0.1348,0.9877,0.0065</t>
+  </si>
+  <si>
+    <t>0.0013,0.0038,0.9966,0.0008</t>
+  </si>
+  <si>
+    <t>0.0019,0.0014,0.9960,0.0019</t>
+  </si>
+  <si>
+    <t>0.0032,0.0035,0.9880,0.0099</t>
+  </si>
+  <si>
+    <t>0.3374,0.0114,0.7534,0.0062</t>
+  </si>
+  <si>
+    <t>0.7354,0.0138,0.2687,0.0182</t>
+  </si>
+  <si>
+    <t>0.0413,0.0023,0.9639,0.0042</t>
+  </si>
+  <si>
+    <t>0.1454,0.0195,0.8745,0.0014</t>
+  </si>
+  <si>
+    <t>0.0894,0.3955,0.4536,0.0027</t>
+  </si>
+  <si>
+    <t>0.4102,0.0657,0.5508,0.0057</t>
+  </si>
+  <si>
+    <t>0.7951,0.0035,0.3174,0.0044</t>
+  </si>
+  <si>
+    <t>0.5280,0.0137,0.6206,0.0034</t>
+  </si>
+  <si>
+    <t>0.0161,0.9880,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.0404,0.9694,0.0014,0.0018</t>
+  </si>
+  <si>
+    <t>0.2648,0.8778,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9514,0.0423,0.0088,0.0058</t>
+  </si>
+  <si>
+    <t>0.9380,0.1165,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.7878,0.0183,0.2372,0.0097</t>
+  </si>
+  <si>
+    <t>0.9604,0.0017,0.0283,0.0061</t>
+  </si>
+  <si>
+    <t>0.9799,0.0024,0.0089,0.0021</t>
+  </si>
+  <si>
+    <t>0.3955,0.0105,0.7265,0.0044</t>
+  </si>
+  <si>
+    <t>0.5749,0.0022,0.2911,0.0401</t>
+  </si>
+  <si>
+    <t>0.0022,0.0028,0.9904,0.0080</t>
+  </si>
+  <si>
+    <t>0.0078,0.0163,0.9736,0.0062</t>
+  </si>
+  <si>
+    <t>0.0283,0.2078,0.9290,0.0070</t>
+  </si>
+  <si>
+    <t>0.0080,0.0038,0.9896,0.0015</t>
+  </si>
+  <si>
+    <t>0.0088,0.0268,0.9621,0.0102</t>
+  </si>
+  <si>
+    <t>0.9928,0.0062,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0009,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9776,0.0173,0.0009,0.0029</t>
+  </si>
+  <si>
+    <t>0.9543,0.0375,0.0077,0.0044</t>
+  </si>
+  <si>
+    <t>0.9587,0.0535,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9946,0.0020,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9910,0.0019,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.0052,0.2755,0.9892,0.0036</t>
+  </si>
+  <si>
+    <t>0.0437,0.3130,0.8504,0.0065</t>
+  </si>
+  <si>
+    <t>0.9046,0.0097,0.0819,0.0081</t>
+  </si>
+  <si>
+    <t>0.0009,0.0009,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0098,0.9974,0.0020</t>
+  </si>
+  <si>
+    <t>0.0009,0.0195,0.9972,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.0017,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0089,0.0018,0.9844,0.0023</t>
+  </si>
+  <si>
+    <t>0.0014,0.0044,0.9958,0.0020</t>
+  </si>
+  <si>
+    <t>0.0053,0.0178,0.9849,0.0017</t>
+  </si>
+  <si>
+    <t>0.0187,0.0146,0.9605,0.0094</t>
+  </si>
+  <si>
+    <t>0.9380,0.0012,0.0608,0.0050</t>
+  </si>
+  <si>
+    <t>0.6386,0.0015,0.5367,0.0021</t>
+  </si>
+  <si>
+    <t>0.9744,0.0026,0.0131,0.0036</t>
+  </si>
+  <si>
+    <t>0.9925,0.0018,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9865,0.0155,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9888,0.0038,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9920,0.0042,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0004,0.0002,0.0037</t>
+  </si>
+  <si>
+    <t>0.9949,0.0014,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9892,0.0029,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9946,0.0016,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.0059,0.0803,0.9724,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0033,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.0087,0.9789,0.0076</t>
+  </si>
+  <si>
+    <t>0.0197,0.0175,0.9664,0.0018</t>
+  </si>
+  <si>
+    <t>0.0087,0.0019,0.9908,0.0007</t>
+  </si>
+  <si>
+    <t>0.0255,0.0139,0.9484,0.0379</t>
+  </si>
+  <si>
+    <t>0.1124,0.0194,0.8794,0.0075</t>
+  </si>
+  <si>
+    <t>0.0767,0.0220,0.8878,0.0262</t>
+  </si>
+  <si>
+    <t>0.8752,0.0005,0.0025,0.1854</t>
+  </si>
+  <si>
+    <t>0.0058,0.0040,0.0248,0.9890</t>
+  </si>
+  <si>
+    <t>0.0297,0.0016,0.0022,0.9868</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0009,0.9987</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.0019,0.9986</t>
+  </si>
+  <si>
+    <t>0.9431,0.0140,0.0175,0.0241</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2779,7 +2779,7 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
         <v>323</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2891,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D69" t="s">
         <v>331</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4305,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
         <v>432</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
